--- a/backend/technoeconomic-inputs/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/technoeconomic-inputs/technoeconomic-inputs-Aligned.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="E-Cooking" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="C02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="JUST ACCESS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rest of subsidies or taxes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="C02" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,121 +428,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>3</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>7</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>8</v>
+        <v>2024</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>9</v>
+        <v>2025</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>10</v>
+        <v>2026</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>11</v>
+        <v>2027</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>12</v>
+        <v>2028</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>13</v>
+        <v>2029</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>14</v>
+        <v>2030</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>15</v>
+        <v>2031</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>16</v>
+        <v>2032</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>17</v>
+        <v>2033</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>18</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>276.2950899341188</v>
       </c>
       <c r="E2" t="n">
-        <v>2023</v>
+        <v>306.9920215583297</v>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>346.6170986885546</v>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>386.2421758187795</v>
       </c>
       <c r="H2" t="n">
-        <v>2026</v>
+        <v>425.8672529490044</v>
       </c>
       <c r="I2" t="n">
-        <v>2027</v>
+        <v>465.4923300792293</v>
       </c>
       <c r="J2" t="n">
-        <v>2028</v>
+        <v>505.1174072094542</v>
       </c>
       <c r="K2" t="n">
-        <v>2029</v>
+        <v>554.2837407335862</v>
       </c>
       <c r="L2" t="n">
-        <v>2030</v>
+        <v>603.8457608577949</v>
       </c>
       <c r="M2" t="n">
-        <v>2031</v>
+        <v>653.4077809820035</v>
       </c>
       <c r="N2" t="n">
-        <v>2032</v>
+        <v>702.9698011062121</v>
       </c>
       <c r="O2" t="n">
-        <v>2033</v>
+        <v>752.5318212304207</v>
       </c>
       <c r="P2" t="n">
-        <v>2034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Outputs of the GRID techno-economic analysis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -552,129 +558,129 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Outputs of the GRID techno-economic analysis</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments of generation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>85.05500933447847</v>
+      </c>
+      <c r="E4" t="n">
+        <v>118.2094299501894</v>
+      </c>
+      <c r="F4" t="n">
+        <v>117.0273356506875</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115.8570622941806</v>
+      </c>
+      <c r="H4" t="n">
+        <v>114.6984916712388</v>
+      </c>
+      <c r="I4" t="n">
+        <v>113.5515067545264</v>
+      </c>
+      <c r="J4" t="n">
+        <v>146.0332962271079</v>
+      </c>
+      <c r="K4" t="n">
+        <v>178.0217589516502</v>
+      </c>
+      <c r="L4" t="n">
+        <v>176.2415413621337</v>
+      </c>
+      <c r="M4" t="n">
+        <v>174.4791259485123</v>
+      </c>
+      <c r="N4" t="n">
+        <v>172.7343346890272</v>
+      </c>
+      <c r="O4" t="n">
+        <v>111.4997432462076</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -685,7 +691,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the grid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,40 +700,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>157.1484243094085</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>176.5289425552756</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>174.7636531297229</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>173.0160165984256</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>171.2858564324414</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>169.572997868117</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>194.6271925235088</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>219.2967595527253</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>217.103791957198</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>214.9327540376261</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>212.7834264972498</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>147.7154689577299</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -736,12 +742,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Operation and Maintenence expenses for the generation component</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -750,40 +756,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>38.91719685610443</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>43.54370457728814</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>49.26939467670242</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>54.87621660367068</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>60.36597515263192</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>65.74045090895356</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>71.00140055263351</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>79.25412891639756</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>87.4189369097862</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>95.41252333041541</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>103.2374961289411</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>110.8964282191632</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -797,7 +803,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the grid component</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,40 +812,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9.283698768575498</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>9.763253331221799</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>10.35048271193446</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>10.92499117969976</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>11.48697442983855</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>12.0366255158566</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>12.5741348827113</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13.31863490554612</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13.99811793774234</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>14.66267944580408</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>15.31254991191082</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>15.94795670075083</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -848,77 +854,103 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Outputs of the OFF GRID techno-economic analysis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -984,83 +1016,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Outputs of the OFF GRID techno-economic analysis</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments of generation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.59925643138779</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.3329871476678</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19.13965727619112</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.94826070342921</v>
+      </c>
+      <c r="H10" t="n">
+        <v>18.75877809639492</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18.57119031543098</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.772405630215641</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.8802050762288234</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.8714030254665355</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.8626889952118701</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.8540621052597519</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.211388908491501</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1071,7 +1077,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the grid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1080,40 +1086,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25.6060737747353</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>30.3350454274157</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>30.03169497314155</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>29.73137802341013</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>29.43406424317604</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>29.13972360074428</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>8.604047232577855</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-11.62479664952581</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-11.50854868303055</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-11.39346319620025</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-11.27952856423825</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-1.28828468079372</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1122,12 +1128,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Operation and Maintenence expenses for the generation component</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1136,40 +1142,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>54.64139486373452</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>61.55888079752739</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>70.10281585724547</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>78.46971632768947</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>86.66226850713886</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>94.6831226713665</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>102.5348935254588</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>101.3963456097667</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>96.484787742642</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>91.66132139829884</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>86.92467590206826</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>82.27359718362247</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1183,7 +1189,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the grid component</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1192,40 +1198,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.492772138817795</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1.573318492344177</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.671692951030647</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.767942588694154</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.862100064309288</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.954197596153249</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2.0442669673539</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.944759591037421</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.776030985291415</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.610482475701225</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.44806733320431</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.288739445309764</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1234,77 +1240,103 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1370,7 +1402,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,123 +1415,97 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" t="n">
+        <v>4.647439669628994</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.67206114401157</v>
+      </c>
+      <c r="F16" t="n">
+        <v>19.72990744805655</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27.78775375210153</v>
+      </c>
+      <c r="H16" t="n">
+        <v>35.84560005614651</v>
+      </c>
+      <c r="I16" t="n">
+        <v>43.90344636019148</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51.96129266423645</v>
+      </c>
+      <c r="K16" t="n">
+        <v>67.62653247011426</v>
+      </c>
+      <c r="L16" t="n">
+        <v>83.09813880231894</v>
+      </c>
+      <c r="M16" t="n">
+        <v>98.56974513452363</v>
+      </c>
+      <c r="N16" t="n">
+        <v>114.0413514667283</v>
+      </c>
+      <c r="O16" t="n">
+        <v>129.512957798933</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments for the e-cooking component</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>27.39637832279744</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>46.71750115009898</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>46.25032613859798</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>45.78782287721201</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>45.32994464843989</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>44.8766452019555</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>66.73006820078001</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>88.25316584233383</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>87.3706341839105</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>86.4969278420714</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>85.6319585636507</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>52.84352607826357</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1508,12 +1514,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Investments for the e-cooking component</t>
+          <t>Operation and Maintenence expenses for the e-cooking component</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1522,40 +1528,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2.017159982169337</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4.044025441960708</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6.162531197098948</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>8.238262434590229</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>10.27186279421197</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>12.26396732039782</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>14.21520256978054</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>15.11701328294783</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>14.99437309623205</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>14.8726740119223</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>14.75190947198912</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>14.63207295545341</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1564,134 +1570,78 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the e-cooking component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+        <v>157.1484243094085</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1708,121 +1658,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>3</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>7</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>8</v>
+        <v>2024</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>9</v>
+        <v>2025</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>10</v>
+        <v>2026</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>11</v>
+        <v>2027</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>12</v>
+        <v>2028</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>13</v>
+        <v>2029</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>14</v>
+        <v>2030</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>15</v>
+        <v>2031</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>16</v>
+        <v>2032</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>17</v>
+        <v>2033</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>18</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>22.97846453679182</v>
       </c>
       <c r="E2" t="n">
-        <v>2023</v>
+        <v>37.73108091272367</v>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>57.78052122104766</v>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>77.82996152937166</v>
       </c>
       <c r="H2" t="n">
-        <v>2026</v>
+        <v>97.87940183769565</v>
       </c>
       <c r="I2" t="n">
-        <v>2027</v>
+        <v>117.9288421460196</v>
       </c>
       <c r="J2" t="n">
-        <v>2028</v>
+        <v>137.9782824543436</v>
       </c>
       <c r="K2" t="n">
-        <v>2029</v>
+        <v>141.7304014809748</v>
       </c>
       <c r="L2" t="n">
-        <v>2030</v>
+        <v>144.3511005462927</v>
       </c>
       <c r="M2" t="n">
-        <v>2031</v>
+        <v>146.9717996116106</v>
       </c>
       <c r="N2" t="n">
-        <v>2032</v>
+        <v>149.5924986769286</v>
       </c>
       <c r="O2" t="n">
-        <v>2033</v>
+        <v>152.2131977422465</v>
       </c>
       <c r="P2" t="n">
-        <v>2034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Outputs of the LOCAL techno-economic analysis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1832,129 +1788,129 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Outputs of the GRID techno-economic analysis</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments of the processing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1300982922326831</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2499460592884246</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2474465986955403</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2449721327085849</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2425224113814991</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2400971872676841</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1790172810082277</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1188423056604961</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1176538826038911</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1164773437778523</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1153125703400737</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1075070213959742</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1965,7 +1921,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the transport segment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1974,40 +1930,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.141951789718218</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.207380410625247</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.207380410625247</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.207380410625247</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2.207380410625247</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2.207380410625247</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.810047367503325</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.412714324381402</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.412714324381402</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.412714324381402</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.412714324381402</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.400208200981237</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2016,12 +1972,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Operation and Maintenence expenses for the processing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2030,40 +1986,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4.32143283622375</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>7.242427610496485</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>11.11893988421549</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>14.91719766969906</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>18.63837840548454</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>22.28364380678734</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>25.85414006222353</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>26.43918243919533</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>26.6588713250685</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>26.87152251498028</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>27.07725479396133</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>27.27618527511125</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -2077,7 +2033,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the transport</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2086,40 +2042,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1.853557812689155</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3.330149509089923</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5.285681783651707</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>7.241214058213492</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>9.196746332775277</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>11.15227860733706</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>13.10781088189885</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13.45131552296902</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13.55265896638958</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>13.65400240981013</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>13.75534585323068</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>13.85668929665124</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -2128,57 +2084,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets for processing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2189,7 +2169,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets for transport</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2198,7 +2178,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2264,7 +2244,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Outputs of the OFF GRID techno-economic analysis</t>
+          <t>Outputs of the UPSTREAM techno-economic analysis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2351,7 +2331,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the processing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2360,40 +2340,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1.554001345736514</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2.785245580029246</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.757393124228953</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.729819192986664</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.702521001056797</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.67549579104623</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2.020197674713041</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.374603151655982</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.360857120139422</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.347248548938028</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.333776063448648</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.261204819010093</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -2407,7 +2387,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Investments of the transport segment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2416,40 +2396,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.8801060224178747</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1.579273972835127</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.579273972835127</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.579273972835127</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.579273972835127</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.579273972835127</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.151191236861284</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.7231085008874403</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.7231085008874403</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.7231085008874403</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.7231085008874403</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.7227985423030808</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2463,7 +2443,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the processing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2472,40 +2452,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.7921030105900182</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1.231593709250723</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.80696957022332</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.37071475460554</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.923004338343094</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.464011058930436</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.993905344672197</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3.992620852367193</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.891034424045832</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.79108046220566</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.692736476159888</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.59598026178881</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2519,154 +2499,120 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M$</t>
+          <t>Operation and Maintenence expenses for the transport</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.3426354805394008</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.5217188646773644</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.7597439544227795</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.9977690441681948</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.23579413391361</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.473819223659025</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.71184431340444</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.715086613488429</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.678590425053564</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.6420942366187</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.605598048183835</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
+        <v>1.56910185974897</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>Operation and Maintenence expenses for the import</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.13713206684385</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29.7815198418991</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45.60674376650624</v>
+      </c>
+      <c r="G15" t="n">
+        <v>61.43196769111339</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.25719161572053</v>
+      </c>
+      <c r="I15" t="n">
+        <v>93.08241554032767</v>
+      </c>
+      <c r="J15" t="n">
+        <v>108.9076394649348</v>
+      </c>
+      <c r="K15" t="n">
+        <v>111.8692245703088</v>
+      </c>
+      <c r="L15" t="n">
+        <v>113.9377685750233</v>
+      </c>
+      <c r="M15" t="n">
+        <v>116.0063125797377</v>
+      </c>
+      <c r="N15" t="n">
+        <v>118.0748565844522</v>
+      </c>
+      <c r="O15" t="n">
+        <v>120.1434005891667</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2724,254 +2670,6 @@
         </is>
       </c>
       <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Investments for the e-cooking component</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Operation and Maintenence expenses for the e-cooking component</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2988,126 +2686,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>3</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>7</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>8</v>
+        <v>2024</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>9</v>
+        <v>2025</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>10</v>
+        <v>2026</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>11</v>
+        <v>2027</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>12</v>
+        <v>2028</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>13</v>
+        <v>2029</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>14</v>
+        <v>2030</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>15</v>
+        <v>2031</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>16</v>
+        <v>2032</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>17</v>
+        <v>2033</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>18</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2023</v>
+        <v>-0.1812776526991066</v>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>-0.369190192015907</v>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>-0.5533263527811014</v>
       </c>
       <c r="H2" t="n">
-        <v>2026</v>
+        <v>-0.7337428713117906</v>
       </c>
       <c r="I2" t="n">
-        <v>2027</v>
+        <v>-0.9104957268365877</v>
       </c>
       <c r="J2" t="n">
-        <v>2028</v>
+        <v>-1.083640150963758</v>
       </c>
       <c r="K2" t="n">
-        <v>2029</v>
+        <v>-1.462122049355739</v>
       </c>
       <c r="L2" t="n">
-        <v>2030</v>
+        <v>-1.819613832973765</v>
       </c>
       <c r="M2" t="n">
-        <v>2031</v>
+        <v>-2.169809568714494</v>
       </c>
       <c r="N2" t="n">
-        <v>2032</v>
+        <v>-2.512819428357112</v>
       </c>
       <c r="O2" t="n">
-        <v>2033</v>
+        <v>-2.848752109850007</v>
       </c>
       <c r="P2" t="n">
-        <v>2034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3119,37 +2823,37 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-5.015809241927665</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-7.638379439193769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-10.23459853925617</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-12.80466448883195</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-15.34877391394851</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-17.86712212820167</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-12.58128690200061</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-12.74318727618186</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-12.90315411444875</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-13.06120270465106</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-13.21734823009849</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3158,94 +2862,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Outputs of the GRID techno-economic analysis</t>
+          <t>Biogas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>Biogas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3257,37 +2935,37 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.03016371389880917</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.04731289369604383</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.06428982760245866</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.08109580934746691</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.09773212402933504</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.1142000481691508</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.03966831374111241</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.04033772599787432</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.04099945242422507</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.04165355314316237</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.04230008786859969</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3296,12 +2974,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>Charcoal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3352,12 +3030,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>Charcoal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3369,37 +3047,37 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-3.753055923132036</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-6.349363471682636</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-8.919614118349651</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-11.4640035244632</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-13.98272604616266</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-16.47597474255701</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-16.48028816779554</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-15.76388588671805</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-15.05423562124715</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-14.35128776128379</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-13.65499302402954</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3408,12 +3086,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>Com. Firew.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3425,37 +3103,37 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>11.30835563214527</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>9.886467298556456</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>8.435010362732655</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>6.953535641462519</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.44158792473071</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3.898705900100119</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.29811514896611</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.137911299767279</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.974173562069574</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.80684727848794</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.635877051878465</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3464,174 +3142,124 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">Pellets </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Outputs of the OFF GRID techno-economic analysis</t>
+          <t xml:space="preserve">Pellets </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2996106729934088</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.5241461389681347</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.7441609345560668</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.9597230196183435</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.170899446885919</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.377756373306181</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.124433593925624</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.190009789098831</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.254162017009181</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.316912199382414</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.378281961906481</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>Biomass ICS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3682,12 +3310,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>Ethanol</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3738,12 +3366,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>Ethanol</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3755,506 +3383,40 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.7208681578822498</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1.505179894713921</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-2.273733309993172</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-3.026765138977365</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-3.764508958050876</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-4.487195224229019</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-7.16999081315265</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-8.863014492025954</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-10.52146069824047</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-12.1458516788815</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-13.73670269383989</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Investments for the e-cooking component</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Operation and Maintenence expenses for the e-cooking component</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -4268,121 +3430,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>3</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>7</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>8</v>
+        <v>2024</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>9</v>
+        <v>2025</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>10</v>
+        <v>2026</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>11</v>
+        <v>2027</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>12</v>
+        <v>2028</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>13</v>
+        <v>2029</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>14</v>
+        <v>2030</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>15</v>
+        <v>2031</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>16</v>
+        <v>2032</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>17</v>
+        <v>2033</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>18</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2026</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2027</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2028</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2029</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2031</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2033</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Outputs of the GRID techno-economic analysis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4392,129 +3560,129 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Outputs of the GRID techno-economic analysis</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments of generation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4525,7 +3693,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the grid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4576,12 +3744,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Operation and Maintenence expenses for the generation component</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4637,7 +3805,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the grid component</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4688,77 +3856,103 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Outputs of the OFF GRID techno-economic analysis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4824,83 +4018,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Outputs of the OFF GRID techno-economic analysis</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments of generation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4911,7 +4079,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investments of generation</t>
+          <t>Investments of the grid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4962,12 +4130,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investments of the grid</t>
+          <t>Operation and Maintenence expenses for the generation component</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5023,7 +4191,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the generation component</t>
+          <t>Operation and Maintenence expenses for the grid component</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5074,77 +4242,103 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the grid component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5210,7 +4404,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Outputs of the E-Cooking-Heat fraction techno-economic analysis</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5223,86 +4417,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Investments for the e-cooking component</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M$</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -5348,12 +4516,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Investments for the e-cooking component</t>
+          <t>Operation and Maintenence expenses for the e-cooking component</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5404,134 +4572,78 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operation and Maintenence expenses for the e-cooking component</t>
+          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (D&amp;A) schedule of the assets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/technoeconomic-inputs/technoeconomic-inputs-Aligned.xlsx
+++ b/backend/technoeconomic-inputs/technoeconomic-inputs-Aligned.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="E-Cooking" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rest of subsidies or taxes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="C02" sheetId="4" state="visible" r:id="rId4"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,39 +453,36 @@
         </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="1" t="n">
         <v>2034</v>
       </c>
     </row>
@@ -541,9 +538,6 @@
       <c r="O2" t="n">
         <v>752.5318212304207</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -621,11 +615,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,9 +668,6 @@
       <c r="O4" t="n">
         <v>111.4997432462076</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -735,9 +721,6 @@
       <c r="O5" t="n">
         <v>147.7154689577299</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,9 +774,6 @@
       <c r="O6" t="n">
         <v>110.8964282191632</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -847,9 +827,6 @@
       <c r="O7" t="n">
         <v>15.94795670075083</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -925,11 +902,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1007,11 +979,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1065,9 +1032,6 @@
       <c r="O10" t="n">
         <v>2.211388908491501</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1121,9 +1085,6 @@
       <c r="O11" t="n">
         <v>-1.28828468079372</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1177,9 +1138,6 @@
       <c r="O12" t="n">
         <v>82.27359718362247</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1233,9 +1191,6 @@
       <c r="O13" t="n">
         <v>1.288739445309764</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1311,11 +1266,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1393,11 +1343,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1451,9 +1396,6 @@
       <c r="O16" t="n">
         <v>129.512957798933</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1507,9 +1449,6 @@
       <c r="O17" t="n">
         <v>52.84352607826357</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1563,9 +1502,6 @@
       <c r="O18" t="n">
         <v>14.63207295545341</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1637,11 +1573,6 @@
         </is>
       </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1658,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,39 +1614,36 @@
         </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="1" t="n">
         <v>2034</v>
       </c>
     </row>
@@ -1771,9 +1699,6 @@
       <c r="O2" t="n">
         <v>152.2131977422465</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1851,11 +1776,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1909,9 +1829,6 @@
       <c r="O4" t="n">
         <v>0.1075070213959742</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1965,9 +1882,6 @@
       <c r="O5" t="n">
         <v>1.400208200981237</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2021,9 +1935,6 @@
       <c r="O6" t="n">
         <v>27.27618527511125</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2077,9 +1988,6 @@
       <c r="O7" t="n">
         <v>13.85668929665124</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2155,11 +2063,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2235,11 +2138,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2317,11 +2215,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2375,9 +2268,6 @@
       <c r="O11" t="n">
         <v>1.261204819010093</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2431,9 +2321,6 @@
       <c r="O12" t="n">
         <v>0.7227985423030808</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2487,9 +2374,6 @@
       <c r="O13" t="n">
         <v>3.59598026178881</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2591,9 +2475,6 @@
       <c r="O15" t="n">
         <v>120.1434005891667</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2665,11 +2546,6 @@
         </is>
       </c>
       <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2686,7 +2562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2711,39 +2587,36 @@
         </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="1" t="n">
         <v>2034</v>
       </c>
     </row>
@@ -2799,9 +2672,6 @@
       <c r="O2" t="n">
         <v>-2.848752109850007</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2855,9 +2725,6 @@
       <c r="O3" t="n">
         <v>-13.21734823009849</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2911,9 +2778,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2967,9 +2831,6 @@
       <c r="O5" t="n">
         <v>-0.04230008786859969</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3023,9 +2884,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3079,9 +2937,6 @@
       <c r="O7" t="n">
         <v>-13.65499302402954</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3135,9 +2990,6 @@
       <c r="O8" t="n">
         <v>2.635877051878465</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3191,9 +3043,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3247,9 +3096,6 @@
       <c r="O10" t="n">
         <v>-1.378281961906481</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3303,9 +3149,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3359,9 +3202,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3414,9 +3254,6 @@
       </c>
       <c r="O13" t="n">
         <v>-13.73670269383989</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3430,7 +3267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3455,39 +3292,36 @@
         </is>
       </c>
       <c r="E1" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="P1" s="1" t="n">
         <v>2034</v>
       </c>
     </row>
@@ -3543,9 +3377,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3623,11 +3454,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3681,9 +3507,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3737,9 +3560,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3793,9 +3613,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3849,9 +3666,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3927,11 +3741,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4009,11 +3818,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4067,9 +3871,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4123,9 +3924,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4179,9 +3977,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4235,9 +4030,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4313,11 +4105,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4395,11 +4182,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4453,9 +4235,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4509,9 +4288,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4565,9 +4341,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4639,11 +4412,6 @@
         </is>
       </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
